--- a/backend/src/evolve/Kelsic_Data_foldy/Round_5_top_variants.xlsx
+++ b/backend/src/evolve/Kelsic_Data_foldy/Round_5_top_variants.xlsx
@@ -443,121 +443,121 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>E4N</t>
+          <t>V31Y</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.0115</v>
+        <v>1.007</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>G29T</t>
+          <t>T12R</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.00575</v>
+        <v>0.9778333333333333</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T12M</t>
+          <t>L17N</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.012</v>
+        <v>1.006</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>V32M</t>
+          <t>I47M</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.988</v>
+        <v>0.892</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T49N</t>
+          <t>L14Y</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.91</v>
+        <v>0.9484999999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E27M</t>
+          <t>M21A</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.852</v>
+        <v>0.98625</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G50K</t>
+          <t>L17Q</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.897</v>
+        <v>0.9395</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G29L</t>
+          <t>D61E</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9984999999999999</v>
+        <v>0.8745000000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G29K</t>
+          <t>T54Q</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.011</v>
+        <v>0.964</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>E27L</t>
+          <t>T54K</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8439999999999999</v>
+        <v>0.9339999999999999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>P18M</t>
+          <t>I36R</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.981</v>
+        <v>0.9554999999999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>E4K</t>
+          <t>L14S</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9914999999999999</v>
+        <v>0.9601666666666667</v>
       </c>
     </row>
   </sheetData>

--- a/backend/src/evolve/Kelsic_Data_foldy/Round_5_top_variants.xlsx
+++ b/backend/src/evolve/Kelsic_Data_foldy/Round_5_top_variants.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,121 +443,991 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>V31Y</t>
+          <t>L26F</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.007</v>
+        <v>0.8405</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T12R</t>
+          <t>P59D</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9778333333333333</v>
+        <v>0.946</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>L17N</t>
+          <t>E4A</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.006</v>
+        <v>0.853</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>I47M</t>
+          <t>E15K</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.892</v>
+        <v>0.7635000000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L14Y</t>
+          <t>E4V</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9484999999999999</v>
+        <v>0.9977499999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M21A</t>
+          <t>V68N</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.98625</v>
+        <v>0.948</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>L17Q</t>
+          <t>L14F</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9395</v>
+        <v>0.948</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D61E</t>
+          <t>L14S</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8745000000000001</v>
+        <v>0.9601666666666667</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>T54Q</t>
+          <t>L14I</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.964</v>
+        <v>0.9733333333333333</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>T54K</t>
+          <t>R46M</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9339999999999999</v>
+        <v>0.732</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>I36R</t>
+          <t>K42S</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9554999999999999</v>
+        <v>0.9106666666666667</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>L14S</t>
+          <t>K52N</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9601666666666667</v>
+        <v>0.9735</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>R23Y</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.996</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>E15F</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.9755</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>K42N</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.893</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>M9H</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.7949999999999999</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>E4R</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.8103333333333333</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>N6F</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1.012</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>L26I</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.699</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>K52A</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0.951</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>T58K</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0.9045000000000001</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>H30C</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1.001</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>N19A</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0.998</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>G50N</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0.884</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>A34T</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0.98775</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>F69R</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>0.9329999999999999</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>I36F</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>0.533</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>E25L</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0.9866666666666668</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>K42C</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>0.899</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>K42I</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>0.8843333333333333</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>F69Y</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>0.9935</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>G50Q</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>0.8925000000000001</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>E56G</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>0.9662499999999998</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>G50R</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>0.9025</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>I7N</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0.9715</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>T12W</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>0.997</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>M21E</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0.9695</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>E27P</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>0.7234999999999999</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>K52G</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>0.972</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>G29D</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>0.994</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>R46Y</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>0.7415</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>E27G</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>0.81225</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>T54E</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>0.9464999999999999</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>E27A</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>0.849</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>G50D</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>0.9125000000000001</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>K42G</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>0.9160000000000001</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>K52S</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>0.9644999999999998</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>E15Y</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>0.982</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>T20W</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>0.913</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>K52V</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>0.95775</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>G29E</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>1.001</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>D51E</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>0.893</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>G65A</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>0.9350000000000001</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>L14G</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>0.9595</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>K42A</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>0.9152500000000001</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>E27I</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>0.8353333333333334</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>N19E</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>0.998</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>E27M</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>0.852</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Q10P</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>0.9205</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>T58N</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>0.952</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>K42T</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>0.8965000000000001</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>H35C</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>R46T</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>0.72725</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>R41K</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>0.9295</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>T33D</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>0.9815</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>G29N</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>0.9984999999999999</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>K42L</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>0.8926666666666666</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>T49K</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>0.944</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>I36C</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>0.9984999999999999</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>R46A</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>0.7572500000000001</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>N28D</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>0.8434999999999999</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Q10W</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>0.916</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>R46N</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>0.742</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>T12F</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>0.982</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>H30I</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>0.9903333333333334</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>M40S</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>0.6023333333333334</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>N6W</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>0.846</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>R46V</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>0.653</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>T49I</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>0.926</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>V31G</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>1.004</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>N6H</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>1.007</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>V31W</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>1.012</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>N28G</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>0.83275</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>D61Q</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>0.826</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Q10V</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>0.95625</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>R46Q</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>0.738</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>R46I</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>0.7243333333333334</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>L17S</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>0.9898333333333332</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>K39Y</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>0.3025</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>V13L</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>0.9386666666666666</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>V24L</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>0.9953333333333333</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>R72M</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>0.901</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>L26V</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>0.73875</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>G29Q</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>1.0005</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>E25W</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>K42M</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>0.927</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>H30P</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>0.96875</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>G29A</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>0.9904999999999999</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>I36K</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>0.9744999999999999</v>
       </c>
     </row>
   </sheetData>
